--- a/backend/data/financials_by_company/002294.SZ.xlsx
+++ b/backend/data/financials_by_company/002294.SZ.xlsx
@@ -3366,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EW2"/>
+  <dimension ref="A1:EU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3782,355 +3782,345 @@
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>recommendationMean</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>shortName</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
       <c r="EU1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4222,34 +4212,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>30.38</v>
+        <v>36.44</v>
       </c>
       <c r="T2" t="n">
-        <v>30.23</v>
+        <v>31.29</v>
       </c>
       <c r="U2" t="n">
-        <v>29.25</v>
+        <v>36.52</v>
       </c>
       <c r="V2" t="n">
-        <v>30.8</v>
+        <v>40.08</v>
       </c>
       <c r="W2" t="n">
-        <v>30.38</v>
+        <v>36.44</v>
       </c>
       <c r="X2" t="n">
-        <v>30.23</v>
+        <v>31.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>29.25</v>
+        <v>36.52</v>
       </c>
       <c r="Z2" t="n">
-        <v>30.8</v>
+        <v>40.08</v>
       </c>
       <c r="AA2" t="n">
         <v>0.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AC2" t="n">
         <v>1779753600</v>
@@ -4261,34 +4251,34 @@
         <v>2.51</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.164</v>
+        <v>-0.159</v>
       </c>
       <c r="AG2" t="n">
-        <v>51.3</v>
+        <v>66.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>48.093754</v>
+        <v>62.625004</v>
       </c>
       <c r="AI2" t="n">
-        <v>19349745</v>
+        <v>64877282</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19349745</v>
+        <v>64877282</v>
       </c>
       <c r="AK2" t="n">
-        <v>17731823</v>
+        <v>21040854</v>
       </c>
       <c r="AL2" t="n">
-        <v>16910962</v>
+        <v>30428078</v>
       </c>
       <c r="AM2" t="n">
-        <v>16910962</v>
+        <v>30428078</v>
       </c>
       <c r="AN2" t="n">
-        <v>30.79</v>
+        <v>40.08</v>
       </c>
       <c r="AO2" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -4297,10 +4287,10 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>34314053632</v>
+        <v>44681846784</v>
       </c>
       <c r="AS2" t="n">
-        <v>33868126333</v>
+        <v>38126725497</v>
       </c>
       <c r="AT2" t="n">
         <v>29.25</v>
@@ -4315,19 +4305,19 @@
         <v>6.72743</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.593461</v>
+        <v>9.887781</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.9442</v>
+        <v>37.9068</v>
       </c>
       <c r="AZ2" t="n">
-        <v>52.3667</v>
+        <v>51.41395</v>
       </c>
       <c r="BA2" t="n">
         <v>0.55</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.018104017</v>
+        <v>0.015093305</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4338,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>32849649664</v>
+        <v>43217444864</v>
       </c>
       <c r="BF2" t="n">
         <v>0.14969</v>
@@ -4353,7 +4343,7 @@
         <v>0.61522996</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.13701001</v>
+        <v>0.12967</v>
       </c>
       <c r="BK2" t="n">
         <v>1114816535</v>
@@ -4362,7 +4352,7 @@
         <v>8.206</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.7509139</v>
+        <v>4.884231</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4394,16 +4384,16 @@
         <v>1429833600</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.269</v>
+        <v>9.564</v>
       </c>
       <c r="BX2" t="n">
-        <v>30.832</v>
+        <v>40.564</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.36918604</v>
+        <v>-0.2317099</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CA2" t="n">
         <v>0.55</v>
@@ -4417,261 +4407,253 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>strong_buy</t>
-        </is>
+        <v>40.08</v>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CF2" t="n">
+        <v>1826301056</v>
       </c>
       <c r="CG2" t="n">
-        <v>1826301056</v>
+        <v>1.638</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.638</v>
+        <v>1065423488</v>
       </c>
       <c r="CI2" t="n">
-        <v>1065423488</v>
+        <v>240210912</v>
       </c>
       <c r="CJ2" t="n">
-        <v>240210912</v>
+        <v>1.513</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.513</v>
+        <v>2.336</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.336</v>
+        <v>4518895104</v>
       </c>
       <c r="CM2" t="n">
-        <v>4518895104</v>
+        <v>2.591</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.591</v>
+        <v>4.011</v>
       </c>
       <c r="CO2" t="n">
-        <v>4.011</v>
+        <v>0.03798</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.03798</v>
+        <v>0.07414</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.07414</v>
+        <v>3388284928</v>
       </c>
       <c r="CR2" t="n">
-        <v>3388284928</v>
+        <v>77718200</v>
       </c>
       <c r="CS2" t="n">
-        <v>77718200</v>
+        <v>1068320832</v>
       </c>
       <c r="CT2" t="n">
-        <v>1068320832</v>
+        <v>0.111</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.111</v>
+        <v>0.157</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.157</v>
+        <v>0.7498</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.7498</v>
+        <v>0.23577</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.23577</v>
-      </c>
-      <c r="CY2" t="n">
         <v>0.20059</v>
       </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>002294.SZ</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>002294.SZ</t>
+          <t>en-US</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>en-US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="DE2" t="b">
         <v>0</v>
       </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.40000153</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>29.25 - 30.8</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
+          <t>SHENZHEN SALUBRIS PHARMA CO LTD</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>Shenzhen Salubris Pharmaceuticals Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1252546200000</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>3.6400032</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>36.52 - 40.08</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>17731823</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.5300007</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.052307718</v>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DO2" t="n">
+        <v>21040854</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>10.830002</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.37025648</v>
+      </c>
+      <c r="DR2" t="inlineStr">
         <is>
           <t>29.25 - 70.99</t>
         </is>
       </c>
-      <c r="DO2" t="n">
-        <v>-40.21</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.5664178</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-36.918606</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="DS2" t="n">
+        <v>-30.909996</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.4354134</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-23.17099</v>
+      </c>
+      <c r="DV2" t="n">
         <v>1745319540</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="DW2" t="n">
         <v>1745319540</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="DX2" t="n">
         <v>1744268400</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="DY2" t="n">
         <v>1744268400</v>
       </c>
-      <c r="DV2" t="b">
+      <c r="DZ2" t="b">
         <v>0</v>
       </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1252546200000</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1.3166608</v>
-      </c>
       <c r="EA2" t="n">
-        <v>30.78</v>
+        <v>0.6</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.64</v>
+        <v>2.1732025</v>
       </c>
       <c r="ED2" t="n">
-        <v>-12.164198</v>
+        <v>0.05733015</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.2832559</v>
+        <v>-11.33395</v>
       </c>
       <c r="EF2" t="n">
-        <v>-21.586699</v>
+        <v>-0.22044502</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.41222188</v>
+        <v>15</v>
       </c>
       <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>1.0 - Strong Buy</t>
-        </is>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1783062264</v>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>1782111882</v>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>finmb_48784795</t>
+        </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>SHZ</t>
+          <t>Asia/Shanghai</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>finmb_48784795</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EO2" t="n">
+        <v>28800000</v>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="ES2" t="b">
+      <c r="EQ2" t="b">
         <v>0</v>
       </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>SHENZHEN SALUBRIS PHARMA CO LTD</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>Shenzhen Salubris Pharmaceuticals Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr"/>
+      <c r="ER2" t="n">
+        <v>9.989032</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="ET2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
